--- a/AAII_Financials/Yearly/SCVL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SCVL_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Yearly/SCVL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SCVL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
   <si>
     <t>SCVL</t>
   </si>
@@ -656,199 +656,212 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45325</v>
+      </c>
+      <c r="E7" s="2">
         <v>44954</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44590</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44226</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43862</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43498</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43134</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42763</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42399</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42035</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41671</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41307</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40936</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1175900</v>
+      </c>
+      <c r="E8" s="3">
         <v>1262200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1330400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>976800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1036600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1029700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1019200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1001100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>984000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>940200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>884800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>855000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>762500</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>754500</v>
+      </c>
+      <c r="E9" s="3">
         <v>794100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>803600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>696800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>724700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>720700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>722900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>711900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>693500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>666500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>625500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>597500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>537700</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>421400</v>
+      </c>
+      <c r="E10" s="3">
         <v>468200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>526800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>280000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>311900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>309000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>296300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>289200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>290500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>273700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>259300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>257500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>224900</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -865,8 +878,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -906,9 +920,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -948,9 +965,12 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -958,17 +978,17 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>1300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1200</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
@@ -984,15 +1004,18 @@
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1032,9 +1055,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1048,92 +1074,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1082400</v>
+      </c>
+      <c r="E17" s="3">
         <v>1115800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1122700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>954900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>982300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>979900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>981500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>963200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>937300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>898300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>841100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>806500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>720400</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>93500</v>
+      </c>
+      <c r="E18" s="3">
         <v>146400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>207700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>21900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>54200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>49800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>37700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>37900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>46600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>41900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>43700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>48500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>42100</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1150,28 +1183,29 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E20" s="3">
         <v>1000</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>700</v>
       </c>
       <c r="H20" s="3">
         <v>700</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -1189,53 +1223,59 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>125200</v>
+      </c>
+      <c r="E21" s="3">
         <v>170600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>226400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>38100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>71900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>72400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>61500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>61600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>69800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>61900</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="3">
         <v>64500</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1243,22 +1283,22 @@
         <v>300</v>
       </c>
       <c r="E22" s="3">
+        <v>300</v>
+      </c>
+      <c r="F22" s="3">
         <v>500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>400</v>
-      </c>
-      <c r="G22" s="3">
-        <v>200</v>
       </c>
       <c r="H22" s="3">
         <v>200</v>
       </c>
       <c r="I22" s="3">
+        <v>200</v>
+      </c>
+      <c r="J22" s="3">
         <v>300</v>
-      </c>
-      <c r="J22" s="3">
-        <v>200</v>
       </c>
       <c r="K22" s="3">
         <v>200</v>
@@ -1270,98 +1310,107 @@
         <v>200</v>
       </c>
       <c r="N22" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O22" s="3">
         <v>300</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>96100</v>
+      </c>
+      <c r="E23" s="3">
         <v>147100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>207200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>21600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>54700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>50400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>37400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>37700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>46500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>41700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>43500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>48300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>42000</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E24" s="3">
         <v>37100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>52300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>11800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>12300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>14100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>14200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>17700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>16200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>16600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>18900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>15600</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1401,93 +1450,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>73300</v>
+      </c>
+      <c r="E26" s="3">
         <v>110100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>154900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>16000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>42900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>38000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>23300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>23500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>28800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>25500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>26900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>29300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>26400</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>73300</v>
+      </c>
+      <c r="E27" s="3">
         <v>110100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>154900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>16000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>42900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>37900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>23100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>23000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>28200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>25100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>26400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>28600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>25800</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1527,9 +1585,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1545,15 +1606,15 @@
       <c r="G29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" s="3">
         <v>100</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-4400</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
       </c>
@@ -1569,9 +1630,12 @@
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1611,9 +1675,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1653,29 +1720,32 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1000</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-700</v>
       </c>
       <c r="H32" s="3">
         <v>-700</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -1693,53 +1763,59 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>73300</v>
+      </c>
+      <c r="E33" s="3">
         <v>110100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>154900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>16000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>42900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>38000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>18700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>23000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>28200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>25100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>26400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>28600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>25800</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1779,98 +1855,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>73300</v>
+      </c>
+      <c r="E35" s="3">
         <v>110100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>154900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>16000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>42900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>38000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>18700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>23000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>28200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>25100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>26400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>28600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>25800</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45325</v>
+      </c>
+      <c r="E38" s="2">
         <v>44954</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44590</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44226</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43862</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43498</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43134</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42763</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42399</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42035</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41671</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41307</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40936</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1887,8 +1972,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1905,62 +1991,66 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E41" s="3">
         <v>51400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>117400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>106500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>61900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>67000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>48300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>62900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>68800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>61400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>48300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>45800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>70600</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E42" s="3">
         <v>11600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>15000</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G42" s="3" t="s">
         <v>8</v>
       </c>
@@ -1976,8 +2066,8 @@
       <c r="K42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
+      <c r="L42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
@@ -1988,177 +2078,192 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E43" s="3">
         <v>3100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>14200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2600</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>346400</v>
+      </c>
+      <c r="E44" s="3">
         <v>390400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>285200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>233300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>259500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>257500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>260500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>279600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>292900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>287900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>284800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>272300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>237700</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E45" s="3">
         <v>13300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>10300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5400</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>481300</v>
+      </c>
+      <c r="E46" s="3">
         <v>469700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>442000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>355300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>329600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>337300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>320600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>351800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>370100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>359100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>342500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>328000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>316300</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2198,51 +2303,57 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>502500</v>
+      </c>
+      <c r="E48" s="3">
         <v>460000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>309500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>268000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>282800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>70600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>86300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>96200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>103400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>101300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>90200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>77400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>69200</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2250,11 +2361,11 @@
         <v>44600</v>
       </c>
       <c r="E49" s="3">
+        <v>44600</v>
+      </c>
+      <c r="F49" s="3">
         <v>44000</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G49" s="3" t="s">
         <v>8</v>
       </c>
@@ -2270,8 +2381,8 @@
       <c r="K49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
+      <c r="L49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -2282,9 +2393,12 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2324,9 +2438,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2366,51 +2483,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E52" s="3">
         <v>15400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>16800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>19500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>15900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>10100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>8700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>10500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1100</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2450,51 +2573,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1042000</v>
+      </c>
+      <c r="E54" s="3">
         <v>989800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>812300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>642700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>628400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>418000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>415600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>458500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>481100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>465000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>436900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>407200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>386600</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2511,8 +2640,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2529,50 +2659,54 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>58300</v>
+      </c>
+      <c r="E57" s="3">
         <v>78800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>69100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>57700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>60700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>48700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>41700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>67800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>72100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>68000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>62700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>65000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>61200</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2612,93 +2746,102 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>69600</v>
+      </c>
+      <c r="E59" s="3">
         <v>78400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>84600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>73200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>61800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>22100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>18500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>15800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>15100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>15000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>17000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14500</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>127900</v>
+      </c>
+      <c r="E60" s="3">
         <v>157300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>153700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>130900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>122500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>70800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>56800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>86300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>87900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>83100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>77700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>82000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>75800</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2738,51 +2881,57 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>330800</v>
+      </c>
+      <c r="E62" s="3">
         <v>306900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>206000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>201700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>208500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>42800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>51500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>53300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>53400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>50700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>42300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>32800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>33100</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2822,9 +2971,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2864,9 +3016,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2906,51 +3061,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>458600</v>
+      </c>
+      <c r="E66" s="3">
         <v>464200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>359700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>332600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>331000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>113600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>108300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>139600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>141300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>133800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>120000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>114800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>102900</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2967,8 +3128,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3008,9 +3170,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3050,9 +3215,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3092,9 +3260,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3134,51 +3305,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>714600</v>
+      </c>
+      <c r="E72" s="3">
         <v>653500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>553500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>406700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>395800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>360400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>326700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>312600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>294300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>270700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>250100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>228100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>222200</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3218,9 +3395,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3260,9 +3440,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3302,51 +3485,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>583400</v>
+      </c>
+      <c r="E76" s="3">
         <v>525600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>452500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>310200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>297400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>304400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>307300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>318900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>339800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>331200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>316900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>292400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>283700</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3386,98 +3575,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45325</v>
+      </c>
+      <c r="E80" s="2">
         <v>44954</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44590</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44226</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43862</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43498</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43134</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42763</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42399</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42035</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41671</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41307</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40936</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>73300</v>
+      </c>
+      <c r="E81" s="3">
         <v>110100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>154900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>16000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>42900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>38000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>18700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>23000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>28200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>25100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>26400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>28600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>25800</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3494,50 +3692,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E83" s="3">
         <v>23200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>18800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>16100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>17000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>21800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>23800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>23700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>23100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>20100</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O83" s="3">
         <v>16000</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3577,9 +3779,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3619,9 +3824,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3661,9 +3869,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3703,9 +3914,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3745,51 +3959,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>122800</v>
+      </c>
+      <c r="E89" s="3">
         <v>50400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>147900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>63400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>66900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>74100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>40300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>63800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>58600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>57700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>38600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>25900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>30900</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3806,50 +4026,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-56300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-77300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-31400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-12400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-18500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-19700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-21800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-27900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-33500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-31000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-26000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-21300</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3889,9 +4113,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3931,51 +4158,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-54600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-74000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-119200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-12100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-17800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-19700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-21800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-27700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-32500</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O94" s="3">
         <v>-25800</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3992,50 +4225,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E96" s="3">
         <v>-10000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-8000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-5100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-5700</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-4800</v>
       </c>
       <c r="I96" s="3">
         <v>-4800</v>
       </c>
       <c r="J96" s="3">
-        <v>-5000</v>
+        <v>-4800</v>
       </c>
       <c r="K96" s="3">
         <v>-5000</v>
       </c>
       <c r="L96" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="M96" s="3">
         <v>-4800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-4900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-23500</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4075,9 +4312,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4117,9 +4357,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4159,51 +4402,57 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-42500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-17700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-6700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-54300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-51000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-35400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-47800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-23500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-12100</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O100" s="3">
         <v>-24900</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4234,58 +4483,64 @@
       <c r="L101" s="3">
         <v>0</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>47600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-66100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>10900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>44600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>18800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-14700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>7400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>13100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-24800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>10400</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SCVL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SCVL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
   <si>
     <t>SCVL</t>
   </si>
@@ -975,13 +975,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
+        <v>800</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F14" s="3">
-        <v>1300</v>
+        <v>4500</v>
       </c>
       <c r="G14" s="3">
         <v>3100</v>
@@ -992,8 +992,8 @@
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
+      <c r="J14" s="3">
+        <v>5100</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -1020,25 +1020,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>28800</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>23200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>18800</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>16100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>21800</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>23800</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1081,25 +1081,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1082400</v>
+        <v>1081600</v>
       </c>
       <c r="E17" s="3">
         <v>1115800</v>
       </c>
       <c r="F17" s="3">
-        <v>1122700</v>
+        <v>1118200</v>
       </c>
       <c r="G17" s="3">
-        <v>954900</v>
+        <v>951800</v>
       </c>
       <c r="H17" s="3">
-        <v>982300</v>
+        <v>981100</v>
       </c>
       <c r="I17" s="3">
         <v>979900</v>
       </c>
       <c r="J17" s="3">
-        <v>981500</v>
+        <v>976400</v>
       </c>
       <c r="K17" s="3">
         <v>963200</v>
@@ -1126,25 +1126,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>93500</v>
+        <v>94300</v>
       </c>
       <c r="E18" s="3">
         <v>146400</v>
       </c>
       <c r="F18" s="3">
-        <v>207700</v>
+        <v>212200</v>
       </c>
       <c r="G18" s="3">
-        <v>21900</v>
+        <v>25000</v>
       </c>
       <c r="H18" s="3">
-        <v>54200</v>
+        <v>55400</v>
       </c>
       <c r="I18" s="3">
         <v>49800</v>
       </c>
       <c r="J18" s="3">
-        <v>37700</v>
+        <v>42800</v>
       </c>
       <c r="K18" s="3">
         <v>37900</v>
@@ -1189,26 +1189,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>2900</v>
-      </c>
-      <c r="E20" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>700</v>
-      </c>
-      <c r="I20" s="3">
-        <v>700</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1235,25 +1235,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>125200</v>
+        <v>123100</v>
       </c>
       <c r="E21" s="3">
-        <v>170600</v>
+        <v>169600</v>
       </c>
       <c r="F21" s="3">
-        <v>226400</v>
+        <v>230900</v>
       </c>
       <c r="G21" s="3">
-        <v>38100</v>
+        <v>41100</v>
       </c>
       <c r="H21" s="3">
-        <v>71900</v>
+        <v>72400</v>
       </c>
       <c r="I21" s="3">
-        <v>72400</v>
+        <v>71600</v>
       </c>
       <c r="J21" s="3">
-        <v>61500</v>
+        <v>66600</v>
       </c>
       <c r="K21" s="3">
         <v>61600</v>
@@ -1385,10 +1385,10 @@
         <v>11800</v>
       </c>
       <c r="I24" s="3">
-        <v>12300</v>
+        <v>12200</v>
       </c>
       <c r="J24" s="3">
-        <v>14100</v>
+        <v>18500</v>
       </c>
       <c r="K24" s="3">
         <v>14200</v>
@@ -1475,10 +1475,10 @@
         <v>42900</v>
       </c>
       <c r="I26" s="3">
-        <v>38000</v>
+        <v>38100</v>
       </c>
       <c r="J26" s="3">
-        <v>23300</v>
+        <v>18900</v>
       </c>
       <c r="K26" s="3">
         <v>23500</v>
@@ -1520,10 +1520,10 @@
         <v>42900</v>
       </c>
       <c r="I27" s="3">
-        <v>37900</v>
+        <v>38000</v>
       </c>
       <c r="J27" s="3">
-        <v>23100</v>
+        <v>18700</v>
       </c>
       <c r="K27" s="3">
         <v>23000</v>
@@ -1594,26 +1594,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-4400</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1729,26 +1729,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-700</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-700</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -1790,10 +1790,10 @@
         <v>42900</v>
       </c>
       <c r="I33" s="3">
-        <v>38000</v>
+        <v>38100</v>
       </c>
       <c r="J33" s="3">
-        <v>18700</v>
+        <v>18900</v>
       </c>
       <c r="K33" s="3">
         <v>23000</v>
@@ -1880,10 +1880,10 @@
         <v>42900</v>
       </c>
       <c r="I35" s="3">
-        <v>38000</v>
+        <v>38100</v>
       </c>
       <c r="J35" s="3">
-        <v>18700</v>
+        <v>18900</v>
       </c>
       <c r="K35" s="3">
         <v>23000</v>
@@ -2051,17 +2051,17 @@
       <c r="F42" s="3">
         <v>15000</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>8</v>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>8</v>
@@ -2267,26 +2267,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2358,25 +2358,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>44600</v>
+        <v>57100</v>
       </c>
       <c r="E49" s="3">
-        <v>44600</v>
+        <v>58300</v>
       </c>
       <c r="F49" s="3">
-        <v>44000</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>8</v>
+        <v>56800</v>
+      </c>
+      <c r="G49" s="3">
+        <v>11200</v>
+      </c>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>8</v>
@@ -2493,25 +2493,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>13600</v>
+        <v>1100</v>
       </c>
       <c r="E52" s="3">
-        <v>15400</v>
+        <v>1700</v>
       </c>
       <c r="F52" s="3">
-        <v>16800</v>
+        <v>1300</v>
       </c>
       <c r="G52" s="3">
-        <v>19500</v>
+        <v>2600</v>
       </c>
       <c r="H52" s="3">
-        <v>15900</v>
+        <v>800</v>
       </c>
       <c r="I52" s="3">
-        <v>10100</v>
+        <v>500</v>
       </c>
       <c r="J52" s="3">
-        <v>8700</v>
+        <v>500</v>
       </c>
       <c r="K52" s="3">
         <v>10500</v>
@@ -2669,7 +2669,7 @@
         <v>58300</v>
       </c>
       <c r="E57" s="3">
-        <v>78800</v>
+        <v>78900</v>
       </c>
       <c r="F57" s="3">
         <v>69100</v>
@@ -2711,19 +2711,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>53000</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>58200</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>51600</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>48800</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>43100</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -2756,25 +2756,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>69600</v>
+        <v>6200</v>
       </c>
       <c r="E59" s="3">
-        <v>78400</v>
+        <v>6200</v>
       </c>
       <c r="F59" s="3">
-        <v>84600</v>
+        <v>8000</v>
       </c>
       <c r="G59" s="3">
-        <v>73200</v>
+        <v>7800</v>
       </c>
       <c r="H59" s="3">
-        <v>61800</v>
+        <v>6000</v>
       </c>
       <c r="I59" s="3">
-        <v>22100</v>
+        <v>6700</v>
       </c>
       <c r="J59" s="3">
-        <v>15000</v>
+        <v>6500</v>
       </c>
       <c r="K59" s="3">
         <v>18500</v>
@@ -2846,19 +2846,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>301400</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>285100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>194800</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>182600</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>194100</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -2891,19 +2891,19 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>330800</v>
+        <v>12100</v>
       </c>
       <c r="E62" s="3">
-        <v>306900</v>
+        <v>10000</v>
       </c>
       <c r="F62" s="3">
-        <v>206000</v>
+        <v>11200</v>
       </c>
       <c r="G62" s="3">
-        <v>201700</v>
+        <v>19000</v>
       </c>
       <c r="H62" s="3">
-        <v>208500</v>
+        <v>14400</v>
       </c>
       <c r="I62" s="3">
         <v>42800</v>
@@ -3650,10 +3650,10 @@
         <v>42900</v>
       </c>
       <c r="I81" s="3">
-        <v>38000</v>
+        <v>38100</v>
       </c>
       <c r="J81" s="3">
-        <v>18700</v>
+        <v>18900</v>
       </c>
       <c r="K81" s="3">
         <v>23000</v>
@@ -4232,25 +4232,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-12200</v>
+        <v>12200</v>
       </c>
       <c r="E96" s="3">
-        <v>-10000</v>
+        <v>10000</v>
       </c>
       <c r="F96" s="3">
-        <v>-8000</v>
+        <v>8000</v>
       </c>
       <c r="G96" s="3">
-        <v>-5100</v>
+        <v>5100</v>
       </c>
       <c r="H96" s="3">
-        <v>-5700</v>
+        <v>5700</v>
       </c>
       <c r="I96" s="3">
-        <v>-4800</v>
+        <v>4800</v>
       </c>
       <c r="J96" s="3">
-        <v>-4800</v>
+        <v>4800</v>
       </c>
       <c r="K96" s="3">
         <v>-5000</v>
@@ -4456,26 +4456,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/SCVL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SCVL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
   <si>
     <t>SCVL</t>
   </si>
@@ -656,212 +656,224 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45689</v>
+      </c>
+      <c r="E7" s="2">
         <v>45325</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44954</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44590</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44226</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43862</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43498</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43134</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42763</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42399</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42035</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41671</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41307</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40936</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1202900</v>
+      </c>
+      <c r="E8" s="3">
         <v>1175900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1262200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1330400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>976800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1036600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1029700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1019200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1001100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>984000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>940200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>884800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>855000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>762500</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>774100</v>
+      </c>
+      <c r="E9" s="3">
         <v>754500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>794100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>803600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>696800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>724700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>720700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>722900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>711900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>693500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>666500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>625500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>597500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>537700</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>428800</v>
+      </c>
+      <c r="E10" s="3">
         <v>421400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>468200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>526800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>280000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>311900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>309000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>296300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>289200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>290500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>273700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>259300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>257500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>224900</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -879,8 +891,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -923,9 +936,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -968,36 +984,39 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>600</v>
+      </c>
+      <c r="E14" s="3">
         <v>800</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>4500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>3100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1200</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>5100</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1007,42 +1026,45 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E15" s="3">
         <v>28800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>23200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>18800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>16100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>17000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>21800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>23800</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1058,9 +1080,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1075,98 +1100,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1111200</v>
+      </c>
+      <c r="E17" s="3">
         <v>1081600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1115800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1118200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>951800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>981100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>979900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>976400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>963200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>937300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>898300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>841100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>806500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>720400</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>91700</v>
+      </c>
+      <c r="E18" s="3">
         <v>94300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>146400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>212200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>25000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>55400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>49800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>42800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>37900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>46600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>41900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>43700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>48500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>42100</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1184,8 +1216,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1210,8 +1243,8 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
@@ -1226,56 +1259,62 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>122800</v>
+      </c>
+      <c r="E21" s="3">
         <v>123100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>169600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>230900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>41100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>72400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>71600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>66600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>61600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>69800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>61900</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="3">
         <v>64500</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1286,22 +1325,22 @@
         <v>300</v>
       </c>
       <c r="F22" s="3">
+        <v>300</v>
+      </c>
+      <c r="G22" s="3">
         <v>500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>400</v>
-      </c>
-      <c r="H22" s="3">
-        <v>200</v>
       </c>
       <c r="I22" s="3">
         <v>200</v>
       </c>
       <c r="J22" s="3">
+        <v>200</v>
+      </c>
+      <c r="K22" s="3">
         <v>300</v>
-      </c>
-      <c r="K22" s="3">
-        <v>200</v>
       </c>
       <c r="L22" s="3">
         <v>200</v>
@@ -1313,104 +1352,113 @@
         <v>200</v>
       </c>
       <c r="O22" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="P22" s="3">
         <v>300</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>300</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>97500</v>
+      </c>
+      <c r="E23" s="3">
         <v>96100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>147100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>207200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>21600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>54700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>50400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>37400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>37700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>46500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>41700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>43500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>48300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>42000</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E24" s="3">
         <v>22800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>37100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>52300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>11800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>12200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>18500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>14200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>17700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>16200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>16600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>18900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>15600</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1453,99 +1501,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>73800</v>
+      </c>
+      <c r="E26" s="3">
         <v>73300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>110100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>154900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>16000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>42900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>38100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>18900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>23500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>28800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>25500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>26900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>29300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>26400</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>73800</v>
+      </c>
+      <c r="E27" s="3">
         <v>73300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>110100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>154900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>16000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>42900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>38000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>18700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>23000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>28200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>25100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>26400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>28600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>25800</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1588,9 +1645,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1675,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>8</v>
@@ -1633,9 +1693,12 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1678,9 +1741,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1723,9 +1789,12 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1750,8 +1819,8 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -1766,56 +1835,62 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>73800</v>
+      </c>
+      <c r="E33" s="3">
         <v>73300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>110100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>154900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>16000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>42900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>38100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>18900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>23000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>28200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>25100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>26400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>28600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>25800</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1858,104 +1933,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>73800</v>
+      </c>
+      <c r="E35" s="3">
         <v>73300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>110100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>154900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>16000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>42900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>38100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>18900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>23000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>28200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>25100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>26400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>28600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>25800</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45689</v>
+      </c>
+      <c r="E38" s="2">
         <v>45325</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44954</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44590</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44226</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43862</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43498</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43134</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42763</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42399</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42035</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41671</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41307</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40936</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1973,8 +2057,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1992,68 +2077,72 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>108700</v>
+      </c>
+      <c r="E41" s="3">
         <v>99000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>51400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>117400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>106500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>61900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>67000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>48300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>62900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>68800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>61400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>48300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>45800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>70600</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E42" s="3">
         <v>12200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>11600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>15000</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -2063,14 +2152,14 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>8</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
+      <c r="M42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
@@ -2081,189 +2170,204 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>14200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2600</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>385600</v>
+      </c>
+      <c r="E44" s="3">
         <v>346400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>390400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>285200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>233300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>259500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>257500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>260500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>279600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>292900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>287900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>284800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>272300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>237700</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E45" s="3">
         <v>21100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>13300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>10300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>8400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>11500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5400</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>536100</v>
+      </c>
+      <c r="E46" s="3">
         <v>481300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>469700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>442000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>355300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>329600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>337300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>320600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>351800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>370100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>359100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>342500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>328000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>316300</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2288,8 +2392,8 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2306,86 +2410,92 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>516400</v>
+      </c>
+      <c r="E48" s="3">
         <v>502500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>460000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>309500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>268000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>282800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>70600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>86300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>96200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>103400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>101300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>90200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>77400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>69200</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E49" s="3">
         <v>57100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>58300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>56800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11200</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
         <v>0</v>
       </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>8</v>
+      <c r="K49" s="3">
+        <v>0</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="M49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -2396,9 +2506,12 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2441,9 +2554,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2486,54 +2602,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E52" s="3">
         <v>1100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>800</v>
-      </c>
-      <c r="I52" s="3">
-        <v>500</v>
       </c>
       <c r="J52" s="3">
         <v>500</v>
       </c>
       <c r="K52" s="3">
+        <v>500</v>
+      </c>
+      <c r="L52" s="3">
         <v>10500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1100</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2576,54 +2698,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1124100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1042000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>989800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>812300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>642700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>628400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>418000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>415600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>458500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>481100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>465000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>436900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>407200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>386600</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2641,8 +2769,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2660,53 +2789,57 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E57" s="3">
         <v>58300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>78900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>69100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>57700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>60700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>48700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>41700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>67800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>72100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>68000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>62700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>65000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>61200</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2714,20 +2847,20 @@
         <v>53000</v>
       </c>
       <c r="E58" s="3">
+        <v>53000</v>
+      </c>
+      <c r="F58" s="3">
         <v>58200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>51600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>48800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>43100</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
@@ -2749,120 +2882,129 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>6200</v>
+      <c r="D59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E59" s="3">
         <v>6200</v>
       </c>
       <c r="F59" s="3">
+        <v>6200</v>
+      </c>
+      <c r="G59" s="3">
         <v>8000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>18500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>15800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>15100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>15000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>17000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>14500</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>130400</v>
+      </c>
+      <c r="E60" s="3">
         <v>127900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>157300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>153700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>130900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>122500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>70800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>56800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>86300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>87900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>83100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>77700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>82000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>75800</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>315000</v>
+      </c>
+      <c r="E61" s="3">
         <v>301400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>285100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>194800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>182600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>194100</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2884,54 +3026,60 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E62" s="3">
         <v>12100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>11200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>19000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>14400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>42800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>51500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>53300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>53400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>50700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>42300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>32800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>33100</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2974,9 +3122,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3019,9 +3170,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3064,54 +3218,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>475100</v>
+      </c>
+      <c r="E66" s="3">
         <v>458600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>464200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>359700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>332600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>331000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>113600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>108300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>139600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>141300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>133800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>120000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>114800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>102900</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3129,8 +3289,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3173,9 +3334,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3218,9 +3382,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3263,9 +3430,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3308,54 +3478,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3">
         <v>714600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>653500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>553500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>406700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>395800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>360400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>326700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>312600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>294300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>270700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>250100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>228100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>222200</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3398,9 +3574,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3443,9 +3622,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3488,54 +3670,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>649000</v>
+      </c>
+      <c r="E76" s="3">
         <v>583400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>525600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>452500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>310200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>297400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>304400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>307300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>318900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>339800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>331200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>316900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>292400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>283700</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3578,104 +3766,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45689</v>
+      </c>
+      <c r="E80" s="2">
         <v>45325</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44954</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44590</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44226</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43862</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43498</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43134</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42763</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42399</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42035</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41671</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41307</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40936</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>73800</v>
+      </c>
+      <c r="E81" s="3">
         <v>73300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>110100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>154900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>16000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>42900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>38100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>18900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>23000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>28200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>25100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>26400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>28600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>25800</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3693,53 +3890,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E83" s="3">
         <v>28800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>23200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>18800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>16100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>17000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>21800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>23800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>23700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>23100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>20100</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P83" s="3">
         <v>16000</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3782,9 +3983,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3827,9 +4031,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3872,9 +4079,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3917,9 +4127,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3962,54 +4175,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>102600</v>
+      </c>
+      <c r="E89" s="3">
         <v>122800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>50400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>147900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>63400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>66900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>74100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>40300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>63800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>58600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>57700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>38600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>25900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>30900</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4027,53 +4246,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-33200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-56300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-77300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-31400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-12400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-18500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-19700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-21800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-27900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-33500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-31000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-26000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-21300</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4116,9 +4339,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4161,54 +4387,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-77700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-54600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-74000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-119200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-12100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-17800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-19700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-21800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-27700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-32500</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P94" s="3">
         <v>-25800</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4226,53 +4458,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E96" s="3">
         <v>12200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>10000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>8000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>5100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>5700</v>
-      </c>
-      <c r="I96" s="3">
-        <v>4800</v>
       </c>
       <c r="J96" s="3">
         <v>4800</v>
       </c>
       <c r="K96" s="3">
-        <v>-5000</v>
+        <v>4800</v>
       </c>
       <c r="L96" s="3">
         <v>-5000</v>
       </c>
       <c r="M96" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="N96" s="3">
         <v>-4800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-4900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-23500</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4315,9 +4551,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4360,9 +4599,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4405,54 +4647,60 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-20500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-42500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-17700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-6700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-54300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-51000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-35400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-47800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-23500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-12100</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P100" s="3">
         <v>-24900</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4477,8 +4725,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4486,61 +4734,67 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E102" s="3">
         <v>47600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-66100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>10900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>44600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>18800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-14700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>7400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>13100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-24800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>10400</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SCVL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SCVL_YR_FIN.xlsx
@@ -993,11 +993,11 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>600</v>
-      </c>
-      <c r="E14" s="3">
-        <v>800</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
@@ -1107,10 +1107,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1111200</v>
+        <v>1111700</v>
       </c>
       <c r="E17" s="3">
-        <v>1081600</v>
+        <v>1082400</v>
       </c>
       <c r="F17" s="3">
         <v>1115800</v>
@@ -1155,10 +1155,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>91700</v>
+        <v>91200</v>
       </c>
       <c r="E18" s="3">
-        <v>94300</v>
+        <v>93500</v>
       </c>
       <c r="F18" s="3">
         <v>146400</v>
@@ -1271,10 +1271,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>122800</v>
+        <v>122200</v>
       </c>
       <c r="E21" s="3">
-        <v>123100</v>
+        <v>122300</v>
       </c>
       <c r="F21" s="3">
         <v>169600</v>
@@ -2471,7 +2471,7 @@
         <v>59000</v>
       </c>
       <c r="E49" s="3">
-        <v>57100</v>
+        <v>44600</v>
       </c>
       <c r="F49" s="3">
         <v>58300</v>
@@ -2612,10 +2612,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>12700</v>
+        <v>12600</v>
       </c>
       <c r="E52" s="3">
-        <v>1100</v>
+        <v>13600</v>
       </c>
       <c r="F52" s="3">
         <v>1700</v>
@@ -2891,8 +2891,8 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>8</v>
+      <c r="D59" s="3">
+        <v>5900</v>
       </c>
       <c r="E59" s="3">
         <v>6200</v>
@@ -3487,8 +3487,8 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>8</v>
+      <c r="D72" s="3">
+        <v>773400</v>
       </c>
       <c r="E72" s="3">
         <v>714600</v>

--- a/AAII_Financials/Yearly/SCVL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SCVL_YR_FIN.xlsx
@@ -1042,13 +1042,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>31100</v>
+        <v>28400</v>
       </c>
       <c r="E15" s="3">
-        <v>28800</v>
+        <v>25800</v>
       </c>
       <c r="F15" s="3">
-        <v>23200</v>
+        <v>20900</v>
       </c>
       <c r="G15" s="3">
         <v>18800</v>
@@ -1271,13 +1271,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>122200</v>
+        <v>119500</v>
       </c>
       <c r="E21" s="3">
-        <v>122300</v>
+        <v>119300</v>
       </c>
       <c r="F21" s="3">
-        <v>169600</v>
+        <v>167300</v>
       </c>
       <c r="G21" s="3">
         <v>230900</v>
@@ -2468,10 +2468,10 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>59000</v>
+        <v>70200</v>
       </c>
       <c r="E49" s="3">
-        <v>44600</v>
+        <v>57100</v>
       </c>
       <c r="F49" s="3">
         <v>58300</v>
@@ -2612,10 +2612,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>12600</v>
+        <v>1500</v>
       </c>
       <c r="E52" s="3">
-        <v>13600</v>
+        <v>1100</v>
       </c>
       <c r="F52" s="3">
         <v>1700</v>
@@ -3897,13 +3897,13 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>31100</v>
+        <v>28400</v>
       </c>
       <c r="E83" s="3">
-        <v>28800</v>
+        <v>25800</v>
       </c>
       <c r="F83" s="3">
-        <v>23200</v>
+        <v>20900</v>
       </c>
       <c r="G83" s="3">
         <v>18800</v>

--- a/AAII_Financials/Yearly/SCVL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SCVL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
   <si>
     <t>SCVL</t>
   </si>
@@ -656,224 +656,237 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E7" s="2">
         <v>45689</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45325</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44954</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44590</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44226</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43862</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43498</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43134</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42763</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42399</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42035</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41671</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41307</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40936</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1135300</v>
+      </c>
+      <c r="E8" s="3">
         <v>1202900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1175900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1262200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1330400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>976800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1036600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1029700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1019200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1001100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>984000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>940200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>884800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>855000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>762500</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>720200</v>
+      </c>
+      <c r="E9" s="3">
         <v>774100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>754500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>794100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>803600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>696800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>724700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>720700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>722900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>711900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>693500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>666500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>625500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>597500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>537700</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>415200</v>
+      </c>
+      <c r="E10" s="3">
         <v>428800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>421400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>468200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>526800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>280000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>311900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>309000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>296300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>289200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>290500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>273700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>259300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>257500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>224900</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -892,8 +905,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -939,9 +953,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -987,9 +1004,12 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1002,24 +1022,24 @@
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
         <v>4500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1200</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>5100</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1029,45 +1049,48 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E15" s="3">
         <v>28400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>25800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>20900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>18800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>16100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>17000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>21800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>23800</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1083,9 +1106,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1101,104 +1127,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1068600</v>
+      </c>
+      <c r="E17" s="3">
         <v>1111700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1082400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1115800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1118200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>951800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>981100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>979900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>976400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>963200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>937300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>898300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>841100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>806500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>720400</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>66800</v>
+      </c>
+      <c r="E18" s="3">
         <v>91200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>93500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>146400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>212200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>25000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>55400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>49800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>42800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>37900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>46600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>41900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>43700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>48500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>42100</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1217,16 +1250,17 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>8</v>
+      <c r="E20" s="3">
+        <v>-3000</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>8</v>
@@ -1246,8 +1280,8 @@
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1262,64 +1296,70 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>119500</v>
+        <v>98300</v>
       </c>
       <c r="E21" s="3">
+        <v>122600</v>
+      </c>
+      <c r="F21" s="3">
         <v>119300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>167300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>230900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>41100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>72400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>71600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>66600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>61600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>69800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>61900</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="3">
         <v>64500</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E22" s="3">
         <v>300</v>
@@ -1328,22 +1368,22 @@
         <v>300</v>
       </c>
       <c r="G22" s="3">
+        <v>300</v>
+      </c>
+      <c r="H22" s="3">
         <v>500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>400</v>
-      </c>
-      <c r="I22" s="3">
-        <v>200</v>
       </c>
       <c r="J22" s="3">
         <v>200</v>
       </c>
       <c r="K22" s="3">
+        <v>200</v>
+      </c>
+      <c r="L22" s="3">
         <v>300</v>
-      </c>
-      <c r="L22" s="3">
-        <v>200</v>
       </c>
       <c r="M22" s="3">
         <v>200</v>
@@ -1355,110 +1395,119 @@
         <v>200</v>
       </c>
       <c r="P22" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q22" s="3">
         <v>300</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>300</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>70400</v>
+      </c>
+      <c r="E23" s="3">
         <v>97500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>96100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>147100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>207200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>21600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>54700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>50400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>37400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>37700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>46500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>41700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>43500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>48300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>42000</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E24" s="3">
         <v>23700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>22800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>37100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>52300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>11800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>12200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>18500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>14200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>17700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>16200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>16600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>18900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>15600</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1504,105 +1553,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>52300</v>
+      </c>
+      <c r="E26" s="3">
         <v>73800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>73300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>110100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>154900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>16000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>42900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>38100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>18900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>23500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>28800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>25500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>26900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>29300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>26400</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>52300</v>
+      </c>
+      <c r="E27" s="3">
         <v>73800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>73300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>110100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>154900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>16000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>42900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>38000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>18700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>23000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>28200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>25100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>26400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>28600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>25800</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1648,9 +1706,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1678,8 +1739,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
@@ -1696,9 +1757,12 @@
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1744,9 +1808,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1792,17 +1859,20 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>8</v>
+      <c r="E32" s="3">
+        <v>3000</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>8</v>
@@ -1822,8 +1892,8 @@
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -1838,59 +1908,65 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>52300</v>
+      </c>
+      <c r="E33" s="3">
         <v>73800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>73300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>110100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>154900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>16000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>42900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>38100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>18900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>23000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>28200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>25100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>26400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>28600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>25800</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1936,110 +2012,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>52300</v>
+      </c>
+      <c r="E35" s="3">
         <v>73800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>73300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>110100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>154900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>16000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>42900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>38100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>18900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>23000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>28200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>25100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>26400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>28600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>25800</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E38" s="2">
         <v>45689</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45325</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44954</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44590</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44226</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43862</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43498</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43134</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42763</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42399</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42035</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41671</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41307</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40936</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2058,8 +2143,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2078,74 +2164,78 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>117100</v>
+      </c>
+      <c r="E41" s="3">
         <v>108700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>99000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>51400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>117400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>106500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>61900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>67000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>48300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>62900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>68800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>61400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>48300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>45800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>70600</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E42" s="3">
         <v>14400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>12200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>11600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>15000</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
@@ -2155,14 +2245,14 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>8</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -2173,201 +2263,216 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E43" s="3">
         <v>9000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>14200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2600</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>439600</v>
+      </c>
+      <c r="E44" s="3">
         <v>385600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>346400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>390400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>285200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>233300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>259500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>257500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>260500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>279600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>292900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>287900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>284800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>272300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>237700</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E45" s="3">
         <v>18400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>21100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>10300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>8400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>11500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5400</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>596100</v>
+      </c>
+      <c r="E46" s="3">
         <v>536100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>481300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>469700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>442000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>355300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>329600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>337300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>320600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>351800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>370100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>359100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>342500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>328000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>316300</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2395,8 +2500,8 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2413,92 +2518,98 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>535200</v>
+      </c>
+      <c r="E48" s="3">
         <v>516400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>502500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>460000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>309500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>268000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>282800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>70600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>86300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>96200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>103400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>101300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>90200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>77400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>69200</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>68400</v>
+      </c>
+      <c r="E49" s="3">
         <v>70200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>57100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>58300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>56800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11200</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>8</v>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="N49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
@@ -2509,9 +2620,12 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2557,9 +2671,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2605,57 +2722,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>800</v>
-      </c>
-      <c r="J52" s="3">
-        <v>500</v>
       </c>
       <c r="K52" s="3">
         <v>500</v>
       </c>
       <c r="L52" s="3">
+        <v>500</v>
+      </c>
+      <c r="M52" s="3">
         <v>10500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1100</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2701,57 +2824,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1201700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1124100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1042000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>989800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>812300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>642700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>628400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>418000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>415600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>458500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>481100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>465000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>436900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>407200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>386600</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2770,8 +2899,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2790,80 +2920,84 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>79200</v>
+      </c>
+      <c r="E57" s="3">
         <v>52000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>58300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>78900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>69100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>57700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>60700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>48700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>41700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>67800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>72100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>68000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>62700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>65000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>61200</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>53000</v>
+        <v>58100</v>
       </c>
       <c r="E58" s="3">
         <v>53000</v>
       </c>
       <c r="F58" s="3">
+        <v>53000</v>
+      </c>
+      <c r="G58" s="3">
         <v>58200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>51600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>48800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>43100</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
@@ -2885,129 +3019,138 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E59" s="3">
         <v>5900</v>
-      </c>
-      <c r="E59" s="3">
-        <v>6200</v>
       </c>
       <c r="F59" s="3">
         <v>6200</v>
       </c>
       <c r="G59" s="3">
+        <v>6200</v>
+      </c>
+      <c r="H59" s="3">
         <v>8000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>18500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>15800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>15100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>15000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>17000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14500</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>158400</v>
+      </c>
+      <c r="E60" s="3">
         <v>130400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>127900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>157300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>153700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>130900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>122500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>70800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>56800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>86300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>87900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>83100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>77700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>82000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>75800</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>313400</v>
+      </c>
+      <c r="E61" s="3">
         <v>315000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>301400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>285100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>194800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>182600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>194100</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -3029,57 +3172,63 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E62" s="3">
         <v>10900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>12100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>11200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>19000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>14400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>42800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>51500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>53300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>53400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>50700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>42300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>32800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>33100</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3125,9 +3274,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3173,9 +3325,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3221,57 +3376,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>512100</v>
+      </c>
+      <c r="E66" s="3">
         <v>475100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>458600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>464200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>359700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>332600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>331000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>113600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>108300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>139600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>141300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>133800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>120000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>114800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>102900</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3290,8 +3451,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3337,9 +3499,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3385,9 +3550,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3433,9 +3601,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3481,57 +3652,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>808800</v>
+      </c>
+      <c r="E72" s="3">
         <v>773400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>714600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>653500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>553500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>406700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>395800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>360400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>326700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>312600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>294300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>270700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>250100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>228100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>222200</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3577,9 +3754,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3625,9 +3805,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3673,57 +3856,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>689700</v>
+      </c>
+      <c r="E76" s="3">
         <v>649000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>583400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>525600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>452500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>310200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>297400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>304400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>307300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>318900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>339800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>331200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>316900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>292400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>283700</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3769,110 +3958,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E80" s="2">
         <v>45689</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45325</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44954</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44590</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44226</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43862</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43498</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43134</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42763</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42399</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42035</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41671</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41307</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40936</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>52300</v>
+      </c>
+      <c r="E81" s="3">
         <v>73800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>73300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>110100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>154900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>16000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>42900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>38100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>18900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>23000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>28200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>25100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>26400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>28600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>25800</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3891,56 +4089,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E83" s="3">
         <v>28400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>25800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>20900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>18800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>16100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>17000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>21800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>23800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>23700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>23100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>20100</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q83" s="3">
         <v>16000</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3986,9 +4188,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4034,9 +4239,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4082,9 +4290,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4130,9 +4341,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4178,57 +4392,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>71300</v>
+      </c>
+      <c r="E89" s="3">
         <v>102600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>122800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>50400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>147900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>63400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>66900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>74100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>40300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>63800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>58600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>57700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>38600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>25900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>30900</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4247,56 +4467,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-44700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-33200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-56300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-77300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-31400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-12400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-18500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-19700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-21800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-27900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-33500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-31000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-26000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-21300</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4342,9 +4566,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4390,57 +4617,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-77700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-54600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-74000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-119200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-12100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-17800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-19700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-21800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-27700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-32500</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-25800</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4459,56 +4692,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E96" s="3">
         <v>14700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>12200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>10000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>8000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>5100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>5700</v>
-      </c>
-      <c r="J96" s="3">
-        <v>4800</v>
       </c>
       <c r="K96" s="3">
         <v>4800</v>
       </c>
       <c r="L96" s="3">
-        <v>-5000</v>
+        <v>4800</v>
       </c>
       <c r="M96" s="3">
         <v>-5000</v>
       </c>
       <c r="N96" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="O96" s="3">
         <v>-4800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-4900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-23500</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4554,9 +4791,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4602,9 +4842,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4650,57 +4893,63 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-15300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-20500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-42500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-17700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-6700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-54300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-51000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-35400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-47800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-23500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-12100</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-24900</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4728,8 +4977,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4737,64 +4986,70 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E102" s="3">
         <v>9700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>47600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-66100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>10900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>44600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>18800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-14700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>7400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>13100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-24800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>10400</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
